--- a/artfynd/A 13630-2025 artfynd.xlsx
+++ b/artfynd/A 13630-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1689,6 +1689,269 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123689953</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57481</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bastuskär, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>767457</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7073271</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre död gran med 4 toppar</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Roger Olofsson, Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123689952</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57481</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bastuskär, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>767477</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7073216</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Trummande och födosökande, flyttade runt mellan olika träd.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Roger Olofsson, Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13630-2025 artfynd.xlsx
+++ b/artfynd/A 13630-2025 artfynd.xlsx
@@ -1572,7 +1572,7 @@
         <v>123605311</v>
       </c>
       <c r="B9" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1691,10 +1691,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123689953</v>
+        <v>123689952</v>
       </c>
       <c r="B10" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1724,12 +1724,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1739,10 +1747,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>767457</v>
+        <v>767477</v>
       </c>
       <c r="R10" t="n">
-        <v>7073271</v>
+        <v>7073216</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1772,14 +1780,24 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Äldre död gran med 4 toppar</t>
+          <t>Trummande och födosökande, flyttade runt mellan olika träd.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1790,21 +1808,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1821,10 +1824,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123689952</v>
+        <v>123689953</v>
       </c>
       <c r="B11" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1854,20 +1857,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1877,10 +1872,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>767477</v>
+        <v>767457</v>
       </c>
       <c r="R11" t="n">
-        <v>7073216</v>
+        <v>7073271</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1910,24 +1905,14 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Trummande och födosökande, flyttade runt mellan olika träd.</t>
+          <t>Äldre död gran med 4 toppar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1938,6 +1923,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">

--- a/artfynd/A 13630-2025 artfynd.xlsx
+++ b/artfynd/A 13630-2025 artfynd.xlsx
@@ -1572,7 +1572,7 @@
         <v>123605311</v>
       </c>
       <c r="B9" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>123689952</v>
       </c>
       <c r="B10" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>123689953</v>
       </c>
       <c r="B11" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 13630-2025 artfynd.xlsx
+++ b/artfynd/A 13630-2025 artfynd.xlsx
@@ -1572,7 +1572,7 @@
         <v>123605311</v>
       </c>
       <c r="B9" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1691,10 +1691,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123689952</v>
+        <v>123689953</v>
       </c>
       <c r="B10" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1724,20 +1724,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1747,10 +1739,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>767477</v>
+        <v>767457</v>
       </c>
       <c r="R10" t="n">
-        <v>7073216</v>
+        <v>7073271</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1780,24 +1772,14 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Trummande och födosökande, flyttade runt mellan olika träd.</t>
+          <t>Äldre död gran med 4 toppar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1808,6 +1790,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1824,10 +1821,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123689953</v>
+        <v>123689952</v>
       </c>
       <c r="B11" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1857,12 +1854,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1872,10 +1877,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>767457</v>
+        <v>767477</v>
       </c>
       <c r="R11" t="n">
-        <v>7073271</v>
+        <v>7073216</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1905,14 +1910,24 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre död gran med 4 toppar</t>
+          <t>Trummande och födosökande, flyttade runt mellan olika träd.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1923,21 +1938,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">

--- a/artfynd/A 13630-2025 artfynd.xlsx
+++ b/artfynd/A 13630-2025 artfynd.xlsx
@@ -1691,7 +1691,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123689953</v>
+        <v>123689952</v>
       </c>
       <c r="B10" t="n">
         <v>57491</v>
@@ -1724,12 +1724,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1739,10 +1747,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>767457</v>
+        <v>767477</v>
       </c>
       <c r="R10" t="n">
-        <v>7073271</v>
+        <v>7073216</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1772,14 +1780,24 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Äldre död gran med 4 toppar</t>
+          <t>Trummande och födosökande, flyttade runt mellan olika träd.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1790,21 +1808,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1821,7 +1824,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123689952</v>
+        <v>123689953</v>
       </c>
       <c r="B11" t="n">
         <v>57491</v>
@@ -1854,20 +1857,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1877,10 +1872,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>767477</v>
+        <v>767457</v>
       </c>
       <c r="R11" t="n">
-        <v>7073216</v>
+        <v>7073271</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1910,24 +1905,14 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Trummande och födosökande, flyttade runt mellan olika träd.</t>
+          <t>Äldre död gran med 4 toppar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1938,6 +1923,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">

--- a/artfynd/A 13630-2025 artfynd.xlsx
+++ b/artfynd/A 13630-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1952,6 +1952,429 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125081449</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bastuskär, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>767395</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7073355</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125081451</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bastuskär, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>767413</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7073412</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125081450</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bastuskär, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>767472</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7073250</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125424548</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90977</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bastuskäret, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>767439</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7073238</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13630-2025 artfynd.xlsx
+++ b/artfynd/A 13630-2025 artfynd.xlsx
@@ -2163,10 +2163,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125081450</v>
+        <v>125424548</v>
       </c>
       <c r="B14" t="n">
-        <v>91030</v>
+        <v>90977</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2175,41 +2175,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bastuskär, Vb</t>
+          <t>Bastuskäret, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>767472</v>
+        <v>767439</v>
       </c>
       <c r="R14" t="n">
-        <v>7073250</v>
+        <v>7073238</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2233,12 +2233,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2265,10 +2275,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125424548</v>
+        <v>125081450</v>
       </c>
       <c r="B15" t="n">
-        <v>90977</v>
+        <v>91030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2277,41 +2287,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bastuskäret, Vb</t>
+          <t>Bastuskär, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>767439</v>
+        <v>767472</v>
       </c>
       <c r="R15" t="n">
-        <v>7073238</v>
+        <v>7073250</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2335,22 +2345,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>09:41</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>09:41</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 13630-2025 artfynd.xlsx
+++ b/artfynd/A 13630-2025 artfynd.xlsx
@@ -1954,10 +1954,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125081449</v>
+        <v>125081451</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1970,39 +1970,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bastuskär, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>767395</v>
+        <v>767413</v>
       </c>
       <c r="R12" t="n">
-        <v>7073355</v>
+        <v>7073412</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -2061,10 +2056,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125081451</v>
+        <v>125081450</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>91184</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2077,21 +2072,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2101,10 +2096,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>767413</v>
+        <v>767472</v>
       </c>
       <c r="R13" t="n">
-        <v>7073412</v>
+        <v>7073250</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2166,7 +2161,7 @@
         <v>125424548</v>
       </c>
       <c r="B14" t="n">
-        <v>90977</v>
+        <v>91131</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2275,10 +2270,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125081450</v>
+        <v>125081449</v>
       </c>
       <c r="B15" t="n">
-        <v>91030</v>
+        <v>57635</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2291,34 +2286,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bastuskär, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>767472</v>
+        <v>767395</v>
       </c>
       <c r="R15" t="n">
-        <v>7073250</v>
+        <v>7073355</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 13630-2025 artfynd.xlsx
+++ b/artfynd/A 13630-2025 artfynd.xlsx
@@ -1954,10 +1954,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125081451</v>
+        <v>125081450</v>
       </c>
       <c r="B12" t="n">
-        <v>78947</v>
+        <v>91184</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>767413</v>
+        <v>767472</v>
       </c>
       <c r="R12" t="n">
-        <v>7073412</v>
+        <v>7073250</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -2056,10 +2056,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125081450</v>
+        <v>125081451</v>
       </c>
       <c r="B13" t="n">
-        <v>91184</v>
+        <v>78947</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2072,21 +2072,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>767472</v>
+        <v>767413</v>
       </c>
       <c r="R13" t="n">
-        <v>7073250</v>
+        <v>7073412</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 13630-2025 artfynd.xlsx
+++ b/artfynd/A 13630-2025 artfynd.xlsx
@@ -1954,53 +1954,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125081450</v>
+        <v>125424548</v>
       </c>
       <c r="B12" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91185</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bastuskär, Vb</t>
+          <t>Bastuskäret, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>767472</v>
+        <v>767439</v>
       </c>
       <c r="R12" t="n">
-        <v>7073250</v>
+        <v>7073238</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2024,12 +2019,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2056,15 +2061,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125081451</v>
+        <v>125081450</v>
       </c>
       <c r="B13" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91238</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2072,21 +2072,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>767413</v>
+        <v>767472</v>
       </c>
       <c r="R13" t="n">
-        <v>7073412</v>
+        <v>7073250</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2158,53 +2158,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125424548</v>
+        <v>125081449</v>
       </c>
       <c r="B14" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bastuskäret, Vb</t>
+          <t>Bastuskär, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>767439</v>
+        <v>767395</v>
       </c>
       <c r="R14" t="n">
-        <v>7073238</v>
+        <v>7073355</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2228,22 +2228,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>09:41</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>09:41</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2270,15 +2260,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125081449</v>
+        <v>125081451</v>
       </c>
       <c r="B15" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2286,39 +2271,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bastuskär, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>767395</v>
+        <v>767413</v>
       </c>
       <c r="R15" t="n">
-        <v>7073355</v>
+        <v>7073412</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 13630-2025 artfynd.xlsx
+++ b/artfynd/A 13630-2025 artfynd.xlsx
@@ -1954,48 +1954,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125424548</v>
+        <v>125081450</v>
       </c>
       <c r="B12" t="n">
-        <v>91185</v>
+        <v>91245</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bastuskäret, Vb</t>
+          <t>Bastuskär, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>767439</v>
+        <v>767472</v>
       </c>
       <c r="R12" t="n">
-        <v>7073238</v>
+        <v>7073250</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2019,22 +2019,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:41</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:41</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2061,48 +2051,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125081450</v>
+        <v>125424548</v>
       </c>
       <c r="B13" t="n">
-        <v>91238</v>
+        <v>91192</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bastuskär, Vb</t>
+          <t>Bastuskäret, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>767472</v>
+        <v>767439</v>
       </c>
       <c r="R13" t="n">
-        <v>7073250</v>
+        <v>7073238</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2126,12 +2116,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 13630-2025 artfynd.xlsx
+++ b/artfynd/A 13630-2025 artfynd.xlsx
@@ -1954,48 +1954,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125081450</v>
+        <v>125424548</v>
       </c>
       <c r="B12" t="n">
-        <v>91245</v>
+        <v>91193</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bastuskär, Vb</t>
+          <t>Bastuskäret, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>767472</v>
+        <v>767439</v>
       </c>
       <c r="R12" t="n">
-        <v>7073250</v>
+        <v>7073238</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2019,12 +2019,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2051,48 +2061,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125424548</v>
+        <v>125081450</v>
       </c>
       <c r="B13" t="n">
-        <v>91192</v>
+        <v>91246</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bastuskäret, Vb</t>
+          <t>Bastuskär, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>767439</v>
+        <v>767472</v>
       </c>
       <c r="R13" t="n">
-        <v>7073238</v>
+        <v>7073250</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2116,22 +2126,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:41</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:41</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2263,7 +2263,7 @@
         <v>125081451</v>
       </c>
       <c r="B15" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 13630-2025 artfynd.xlsx
+++ b/artfynd/A 13630-2025 artfynd.xlsx
@@ -1954,48 +1954,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125424548</v>
+        <v>125081450</v>
       </c>
       <c r="B12" t="n">
-        <v>91193</v>
+        <v>91250</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bastuskäret, Vb</t>
+          <t>Bastuskär, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>767439</v>
+        <v>767472</v>
       </c>
       <c r="R12" t="n">
-        <v>7073238</v>
+        <v>7073250</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2019,22 +2019,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:41</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:41</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2061,48 +2051,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125081450</v>
+        <v>125424548</v>
       </c>
       <c r="B13" t="n">
-        <v>91246</v>
+        <v>91197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bastuskär, Vb</t>
+          <t>Bastuskäret, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>767472</v>
+        <v>767439</v>
       </c>
       <c r="R13" t="n">
-        <v>7073250</v>
+        <v>7073238</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2126,12 +2116,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2263,7 +2263,7 @@
         <v>125081451</v>
       </c>
       <c r="B15" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 13630-2025 artfynd.xlsx
+++ b/artfynd/A 13630-2025 artfynd.xlsx
@@ -1954,48 +1954,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125081450</v>
+        <v>125424548</v>
       </c>
       <c r="B12" t="n">
-        <v>91250</v>
+        <v>91197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bastuskär, Vb</t>
+          <t>Bastuskäret, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>767472</v>
+        <v>767439</v>
       </c>
       <c r="R12" t="n">
-        <v>7073250</v>
+        <v>7073238</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2019,12 +2019,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2051,48 +2061,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125424548</v>
+        <v>125081450</v>
       </c>
       <c r="B13" t="n">
-        <v>91197</v>
+        <v>91250</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bastuskäret, Vb</t>
+          <t>Bastuskär, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>767439</v>
+        <v>767472</v>
       </c>
       <c r="R13" t="n">
-        <v>7073238</v>
+        <v>7073250</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2116,22 +2126,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:41</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:41</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 13630-2025 artfynd.xlsx
+++ b/artfynd/A 13630-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2355,6 +2355,545 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127804572</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58033</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bastuskär, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>767460</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7073385</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127804540</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91332</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bastuskär, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>767511</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7073251</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Granlåga knäckt äldre</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga knäckt äldre</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127804538</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91297</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bastuskär, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>767494</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7073270</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Toppknäckt</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies # Toppknäckt</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127804603</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bastuskär, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>767502</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7073265</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127804559</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58093</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bastuskär, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>767460</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7073385</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13630-2025 artfynd.xlsx
+++ b/artfynd/A 13630-2025 artfynd.xlsx
@@ -2462,7 +2462,7 @@
         <v>127804540</v>
       </c>
       <c r="B17" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>127804538</v>
       </c>
       <c r="B18" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 13630-2025 artfynd.xlsx
+++ b/artfynd/A 13630-2025 artfynd.xlsx
@@ -2360,7 +2360,7 @@
         <v>127804572</v>
       </c>
       <c r="B16" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>127804540</v>
       </c>
       <c r="B17" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>127804538</v>
       </c>
       <c r="B18" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>127804603</v>
       </c>
       <c r="B19" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>127804559</v>
       </c>
       <c r="B20" t="n">
-        <v>58093</v>
+        <v>58096</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 13630-2025 artfynd.xlsx
+++ b/artfynd/A 13630-2025 artfynd.xlsx
@@ -2360,7 +2360,7 @@
         <v>127804572</v>
       </c>
       <c r="B16" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>127804540</v>
       </c>
       <c r="B17" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>127804538</v>
       </c>
       <c r="B18" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>127804603</v>
       </c>
       <c r="B19" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>127804559</v>
       </c>
       <c r="B20" t="n">
-        <v>58096</v>
+        <v>58102</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 13630-2025 artfynd.xlsx
+++ b/artfynd/A 13630-2025 artfynd.xlsx
@@ -2462,7 +2462,7 @@
         <v>127804540</v>
       </c>
       <c r="B17" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>127804538</v>
       </c>
       <c r="B18" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 13630-2025 artfynd.xlsx
+++ b/artfynd/A 13630-2025 artfynd.xlsx
@@ -2462,7 +2462,7 @@
         <v>127804540</v>
       </c>
       <c r="B17" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>127804538</v>
       </c>
       <c r="B18" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 13630-2025 artfynd.xlsx
+++ b/artfynd/A 13630-2025 artfynd.xlsx
@@ -2462,7 +2462,7 @@
         <v>127804540</v>
       </c>
       <c r="B17" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>127804538</v>
       </c>
       <c r="B18" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 13630-2025 artfynd.xlsx
+++ b/artfynd/A 13630-2025 artfynd.xlsx
@@ -2360,7 +2360,7 @@
         <v>127804572</v>
       </c>
       <c r="B16" t="n">
-        <v>58042</v>
+        <v>58043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>127804540</v>
       </c>
       <c r="B17" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>127804538</v>
       </c>
       <c r="B18" t="n">
-        <v>91317</v>
+        <v>91325</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>127804603</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>127804559</v>
       </c>
       <c r="B20" t="n">
-        <v>58102</v>
+        <v>58103</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 13630-2025 artfynd.xlsx
+++ b/artfynd/A 13630-2025 artfynd.xlsx
@@ -2360,7 +2360,7 @@
         <v>127804572</v>
       </c>
       <c r="B16" t="n">
-        <v>58043</v>
+        <v>58055</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>127804540</v>
       </c>
       <c r="B17" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>127804538</v>
       </c>
       <c r="B18" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>127804603</v>
       </c>
       <c r="B19" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>127804559</v>
       </c>
       <c r="B20" t="n">
-        <v>58103</v>
+        <v>58115</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
